--- a/data/trans_orig/Q5413-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5413-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de vestirse solo en 2007</t>
+          <t>Población según si es capaz de vestirse solo en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4746</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,62 +768,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5422</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>950</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4650</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -846,97 +846,97 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2080</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55038</t>
+          <t>55061</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27881</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29709</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>84843</t>
+          <t>84071</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1189,97 +1189,97 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1870</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1868</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>11,83%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1904</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1302,97 +1302,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1870</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1868</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>11,83%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1904</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48960</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50830</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13918</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15786</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64712</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66616</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1645,97 +1645,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2177</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1762</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>6554</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>8,97%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>27,0%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>2177</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>6676</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>8,97%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>8321</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>27,5%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>2177</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>6978</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>2,27%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>819</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6276</t>
+          <t>7144</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>806</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7358</t>
+          <t>7092</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>65478</t>
+          <t>64610</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70959</t>
+          <t>70935</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17599</t>
+          <t>17721</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>85238</t>
+          <t>85910</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>94150</t>
+          <t>94237</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,13%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>952</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8606</t>
+          <t>9289</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5867</t>
+          <t>5634</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1894</t>
+          <t>1881</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11053</t>
+          <t>10938</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3541</t>
+          <t>3576</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13438</t>
+          <t>13755</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,82 +2229,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>5,29%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>2220</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>6698</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>7,81%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>9565</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>4694</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>17370</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>2,77%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>1,36%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>5,17%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>2220</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>7570</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>8,83%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>9565</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>4679</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>16624</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>241533</t>
+          <t>241787</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>254303</t>
+          <t>254355</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>76950</t>
+          <t>76781</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>84706</t>
+          <t>84697</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>322745</t>
+          <t>322462</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>337411</t>
+          <t>337307</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1769</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>944</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9641</t>
+          <t>10053</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1217</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10188</t>
+          <t>9984</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10616</t>
+          <t>10212</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1142</t>
+          <t>1123</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9272</t>
+          <t>9508</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3643</t>
+          <t>3896</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>14752</t>
+          <t>15182</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>44849</t>
+          <t>45253</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53578</t>
+          <t>53700</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>81596</t>
+          <t>81236</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>92971</t>
+          <t>92878</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>131653</t>
+          <t>131613</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>144926</t>
+          <t>145016</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,58%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2516</t>
+          <t>2738</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14299</t>
+          <t>15013</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>14458</t>
+          <t>14551</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17395</t>
+          <t>16996</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>4447</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17078</t>
+          <t>17358</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>399219</t>
+          <t>399039</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>415682</t>
+          <t>415523</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>402737</t>
+          <t>402592</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>419119</t>
+          <t>419219</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>1743</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10158</t>
+          <t>9488</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7923</t>
+          <t>8034</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>23670</t>
+          <t>23499</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>12365</t>
+          <t>12459</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>30282</t>
+          <t>30350</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8807</t>
+          <t>8964</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>23124</t>
+          <t>23522</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8374</t>
+          <t>9043</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>24333</t>
+          <t>25025</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>20319</t>
+          <t>20999</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>41502</t>
+          <t>42330</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>472824</t>
+          <t>472869</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>489451</t>
+          <t>488950</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>634702</t>
+          <t>634090</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>657079</t>
+          <t>656918</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1114791</t>
+          <t>1113369</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1141834</t>
+          <t>1141465</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,87%</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de vestirse solo en 2012</t>
+          <t>Población según si es capaz de vestirse solo en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4159,97 +4159,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2151</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2091</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>8,27%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2171</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>5873</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6867</t>
+          <t>6777</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>964</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8884</t>
+          <t>8557</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38666</t>
+          <t>38045</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18422</t>
+          <t>18512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>60323</t>
+          <t>60650</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>68235</t>
+          <t>68243</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -4615,97 +4615,97 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2209</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2230</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>6278</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>11,69%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>33,21%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>2209</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>6676</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>11,69%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>7231</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>35,32%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>2209</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>6520</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7194</t>
+          <t>7656</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4778</t>
+          <t>4680</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9334</t>
+          <t>9974</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,54%</t>
         </is>
       </c>
     </row>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53436</t>
+          <t>52974</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11281</t>
+          <t>11542</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18902</t>
+          <t>17873</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>67592</t>
+          <t>67444</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77333</t>
+          <t>77419</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6176</t>
+          <t>5121</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5091,77 +5091,77 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
+          <t>4,32%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2197</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>7158</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>4,02%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>13,11%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>3189</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>987</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>9024</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
           <t>5,21%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>2197</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>12,29%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>3189</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>988</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>8876</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>1971</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11343</t>
+          <t>10867</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7474</t>
+          <t>7427</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3112</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14002</t>
+          <t>13563</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>106305</t>
+          <t>106234</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>115892</t>
+          <t>115817</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>44410</t>
+          <t>44199</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53465</t>
+          <t>53468</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>154747</t>
+          <t>155611</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>167870</t>
+          <t>168000</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,96%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6235</t>
+          <t>6241</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21800</t>
+          <t>20860</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>5551</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21633</t>
+          <t>22122</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8448</t>
+          <t>9197</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>26657</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2184</t>
+          <t>2625</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11188</t>
+          <t>12954</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12749</t>
+          <t>14358</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32859</t>
+          <t>33696</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,55%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>192176</t>
+          <t>191878</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>214062</t>
+          <t>213508</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>48907</t>
+          <t>47141</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>57911</t>
+          <t>57470</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>245257</t>
+          <t>243028</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>268181</t>
+          <t>269202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>92,24%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>980</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8216</t>
+          <t>8109</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>5409</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18271</t>
+          <t>18984</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>8350</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>23964</t>
+          <t>23401</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11560</t>
+          <t>12217</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>18208</t>
+          <t>17780</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>38154</t>
+          <t>37019</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>23280</t>
+          <t>23147</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>44466</t>
+          <t>44878</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,42%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>87595</t>
+          <t>86682</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>98547</t>
+          <t>98524</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>138238</t>
+          <t>138841</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>159978</t>
+          <t>160519</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>230538</t>
+          <t>230474</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>255888</t>
+          <t>256473</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>88,11%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12728</t>
+          <t>11690</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>30875</t>
+          <t>30989</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>11649</t>
+          <t>13347</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>31922</t>
+          <t>32061</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22662</t>
+          <t>21615</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>46359</t>
+          <t>43831</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>21576</t>
+          <t>21383</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>43762</t>
+          <t>43429</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>325458</t>
+          <t>327180</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>354960</t>
+          <t>355649</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>329558</t>
+          <t>330646</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>357675</t>
+          <t>357398</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,09%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8706</t>
+          <t>9510</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26951</t>
+          <t>25637</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>25507</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>50120</t>
+          <t>48777</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>39365</t>
+          <t>38542</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>68982</t>
+          <t>66976</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>19362</t>
+          <t>19492</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>42030</t>
+          <t>42252</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>55169</t>
+          <t>55208</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>88068</t>
+          <t>88485</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7063,7 +7063,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>82149</t>
+          <t>81033</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>122582</t>
+          <t>120492</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>498213</t>
+          <t>499982</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>526656</t>
+          <t>527631</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>613044</t>
+          <t>615302</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>652646</t>
+          <t>654495</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1123207</t>
+          <t>1123014</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1171374</t>
+          <t>1171562</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,01%</t>
         </is>
       </c>
     </row>
@@ -7390,7 +7390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de vestirse solo en 2016</t>
+          <t>Población según si es capaz de vestirse solo en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7585,97 +7585,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1933</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>6,36%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2085</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>3938</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8434</t>
+          <t>8084</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>745</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9953</t>
+          <t>8686</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64625</t>
+          <t>64709</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>28454</t>
+          <t>28804</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>95582</t>
+          <t>96849</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>104786</t>
+          <t>104790</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>908</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7799</t>
+          <t>7845</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>909</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7842</t>
+          <t>8379</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6119</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6568</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>887</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8705</t>
+          <t>8784</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,38%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43414</t>
+          <t>43034</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51513</t>
+          <t>51423</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11020</t>
+          <t>11984</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57974</t>
+          <t>59146</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68377</t>
+          <t>68909</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>97,15%</t>
         </is>
       </c>
     </row>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5727</t>
+          <t>5757</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,62 +8532,62 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>1656</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2322</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>5958</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>5,03%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>1656</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>5228</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11114</t>
+          <t>10226</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7201</t>
+          <t>7091</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8665,7 +8665,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3239</t>
+          <t>3814</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14293</t>
+          <t>14436</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>106785</t>
+          <t>107382</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>117007</t>
+          <t>117183</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>39008</t>
+          <t>39118</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -8773,7 +8773,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>150139</t>
+          <t>149487</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>161869</t>
+          <t>161446</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>96,98%</t>
         </is>
       </c>
     </row>
@@ -8958,7 +8958,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5791</t>
+          <t>5854</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8993,7 +8993,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6502</t>
+          <t>6636</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>822</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8436</t>
+          <t>7999</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8213</t>
+          <t>7723</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21490</t>
+          <t>20688</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2699</t>
+          <t>2358</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15060</t>
+          <t>15524</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13289</t>
+          <t>13549</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31046</t>
+          <t>30868</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>180394</t>
+          <t>180835</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>194038</t>
+          <t>194411</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>82872</t>
+          <t>81514</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>95667</t>
+          <t>95575</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>268839</t>
+          <t>268655</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>287416</t>
+          <t>287123</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,79%</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4932</t>
+          <t>5841</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9259</t>
+          <t>7976</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10851</t>
+          <t>10027</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>2375</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12803</t>
+          <t>12444</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9542,7 +9542,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6907</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>22400</t>
+          <t>23316</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>11427</t>
+          <t>11951</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>28986</t>
+          <t>30162</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>130525</t>
+          <t>130850</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>141740</t>
+          <t>141776</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>133600</t>
+          <t>132906</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>150448</t>
+          <t>150705</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>269949</t>
+          <t>269265</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>289624</t>
+          <t>289344</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,94%</t>
         </is>
       </c>
     </row>
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8973</t>
+          <t>9370</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>27617</t>
+          <t>27980</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8973</t>
+          <t>9370</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>27617</t>
+          <t>27980</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14861</t>
+          <t>15370</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38669</t>
+          <t>37873</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14861</t>
+          <t>15370</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>38669</t>
+          <t>37873</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>355989</t>
+          <t>356363</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>384748</t>
+          <t>384772</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>355989</t>
+          <t>356363</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>384748</t>
+          <t>384772</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,15%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>3618</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14126</t>
+          <t>14082</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12613</t>
+          <t>12524</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>34265</t>
+          <t>33445</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>19327</t>
+          <t>18696</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>40863</t>
+          <t>41477</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>19524</t>
+          <t>19176</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38092</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>36444</t>
+          <t>36355</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>69132</t>
+          <t>67687</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>61479</t>
+          <t>60992</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>97629</t>
+          <t>101299</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>543110</t>
+          <t>543330</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>565254</t>
+          <t>564893</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>679408</t>
+          <t>681183</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>717375</t>
+          <t>717605</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1234963</t>
+          <t>1231701</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1275467</t>
+          <t>1276778</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,63%</t>
         </is>
       </c>
     </row>
@@ -10816,7 +10816,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de vestirse solo en 2023</t>
+          <t>Población según si es capaz de vestirse solo en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11011,97 +11011,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>942</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1092</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11129,7 +11129,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3547</t>
+          <t>3531</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11164,7 +11164,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3521</t>
+          <t>2908</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11179,7 +11179,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11194,12 +11194,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>334</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4221</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -11237,7 +11237,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>104032</t>
+          <t>104048</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -11252,7 +11252,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61800</t>
+          <t>62413</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -11287,7 +11287,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>168679</t>
+          <t>168661</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>172567</t>
+          <t>172566</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11322,7 +11322,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -11467,12 +11467,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11482,12 +11482,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11502,12 +11502,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>396</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4521</t>
+          <t>4125</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11537,12 +11537,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>386</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11557,7 +11557,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -11580,12 +11580,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8880</t>
+          <t>9594</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11620,7 +11620,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2405</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9666</t>
+          <t>9998</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>86118</t>
+          <t>85404</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>93722</t>
+          <t>93656</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41876</t>
+          <t>42175</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46366</t>
+          <t>46364</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>130591</t>
+          <t>130384</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>138837</t>
+          <t>139239</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>2921</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11963,7 +11963,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3279</t>
+          <t>2985</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11978,7 +11978,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11993,12 +11993,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>354</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4165</t>
+          <t>4143</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12013,7 +12013,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -12036,12 +12036,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2877</t>
+          <t>2837</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10584</t>
+          <t>10704</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12051,12 +12051,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6137</t>
+          <t>6421</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>5412</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14290</t>
+          <t>14272</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>90960</t>
+          <t>90247</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>98751</t>
+          <t>98521</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>46030</t>
+          <t>45683</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51256</t>
+          <t>51105</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>138533</t>
+          <t>139402</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>148316</t>
+          <t>148388</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,82%</t>
         </is>
       </c>
     </row>
@@ -12379,12 +12379,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2074</t>
+          <t>2126</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10276</t>
+          <t>9812</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12394,12 +12394,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12419,7 +12419,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7676</t>
+          <t>7191</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12434,7 +12434,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2284</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14442</t>
+          <t>13911</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12464,12 +12464,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -12492,12 +12492,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8138</t>
+          <t>7836</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19420</t>
+          <t>18906</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12527,12 +12527,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19112</t>
+          <t>19037</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>6779</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32326</t>
+          <t>32650</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>212312</t>
+          <t>213175</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>225751</t>
+          <t>226547</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>302113</t>
+          <t>301617</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>325259</t>
+          <t>325426</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>520952</t>
+          <t>521003</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>555676</t>
+          <t>555638</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,36%</t>
         </is>
       </c>
     </row>
@@ -12840,7 +12840,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12870,12 +12870,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3448</t>
+          <t>3424</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10892</t>
+          <t>10156</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12885,12 +12885,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4472</t>
+          <t>4306</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12377</t>
+          <t>12059</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8142</t>
+          <t>8152</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>16242</t>
+          <t>16126</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>28846</t>
+          <t>28808</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>19877</t>
+          <t>20414</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>33905</t>
+          <t>33405</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13033,12 +13033,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>81934</t>
+          <t>81707</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>88966</t>
+          <t>89045</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>168146</t>
+          <t>168830</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>182380</t>
+          <t>182604</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>254072</t>
+          <t>254300</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>269797</t>
+          <t>269352</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,9%</t>
         </is>
       </c>
     </row>
@@ -13291,12 +13291,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13306,12 +13306,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13326,12 +13326,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6219</t>
+          <t>6413</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15630</t>
+          <t>16527</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13341,12 +13341,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6194</t>
+          <t>6540</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16277</t>
+          <t>16799</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13376,12 +13376,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -13404,12 +13404,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13439,12 +13439,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>25788</t>
+          <t>25112</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>41493</t>
+          <t>41146</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>24513</t>
+          <t>26011</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>41159</t>
+          <t>42126</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -13517,12 +13517,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2358</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13532,12 +13532,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13552,12 +13552,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>268684</t>
+          <t>268759</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>286297</t>
+          <t>286785</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13587,12 +13587,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>272364</t>
+          <t>270663</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>291214</t>
+          <t>289628</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13602,12 +13602,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,15%</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13747,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3609</t>
+          <t>3585</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12232</t>
+          <t>13154</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13762,12 +13762,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10648</t>
+          <t>10330</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>31360</t>
+          <t>30601</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13797,12 +13797,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13817,12 +13817,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>18134</t>
+          <t>18707</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>38571</t>
+          <t>38083</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13832,12 +13832,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -13860,12 +13860,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>19383</t>
+          <t>20492</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>36679</t>
+          <t>36366</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13875,12 +13875,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>34132</t>
+          <t>31354</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>87747</t>
+          <t>84905</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13910,12 +13910,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>58968</t>
+          <t>58060</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>112485</t>
+          <t>113364</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13945,12 +13945,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>593258</t>
+          <t>593665</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>612063</t>
+          <t>611223</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>903770</t>
+          <t>905685</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>971117</t>
+          <t>975032</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1510145</t>
+          <t>1509546</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1579145</t>
+          <t>1577612</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,28%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5413-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5413-Clase-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>4765</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5422</t>
+          <t>5414</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55061</t>
+          <t>55019</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>84071</t>
+          <t>84079</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6554</t>
+          <t>7451</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8321</t>
+          <t>7271</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>805</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7144</t>
+          <t>7344</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>806</t>
+          <t>811</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7092</t>
+          <t>7931</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>64610</t>
+          <t>64410</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70935</t>
+          <t>70949</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17721</t>
+          <t>16824</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>85910</t>
+          <t>85118</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>94237</t>
+          <t>94222</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>879</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9289</t>
+          <t>8627</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5634</t>
+          <t>5668</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10938</t>
+          <t>11267</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3576</t>
+          <t>2966</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13755</t>
+          <t>13659</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6698</t>
+          <t>7816</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4694</t>
+          <t>4961</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17370</t>
+          <t>16485</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>241787</t>
+          <t>241226</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>254355</t>
+          <t>254224</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>76781</t>
+          <t>76558</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>84697</t>
+          <t>84704</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>322462</t>
+          <t>323356</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>337307</t>
+          <t>337426</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10053</t>
+          <t>10460</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>973</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9984</t>
+          <t>10135</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10212</t>
+          <t>9598</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9508</t>
+          <t>9759</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3896</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>15182</t>
+          <t>15570</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>45253</t>
+          <t>45867</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53700</t>
+          <t>53638</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>81236</t>
+          <t>81536</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>92878</t>
+          <t>92874</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>131613</t>
+          <t>131768</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>145016</t>
+          <t>145420</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,85%</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2738</t>
+          <t>2401</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15013</t>
+          <t>14045</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>14551</t>
+          <t>14359</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>4634</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16996</t>
+          <t>17778</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4447</t>
+          <t>4841</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17358</t>
+          <t>17053</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>399039</t>
+          <t>398460</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>415523</t>
+          <t>415505</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>402592</t>
+          <t>401662</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>419219</t>
+          <t>419117</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,76%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1743</t>
+          <t>1780</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9488</t>
+          <t>10436</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8034</t>
+          <t>8251</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>23499</t>
+          <t>24496</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>12459</t>
+          <t>11322</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>30350</t>
+          <t>30135</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8964</t>
+          <t>8969</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>23522</t>
+          <t>23915</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>9043</t>
+          <t>8495</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>25025</t>
+          <t>25341</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>20999</t>
+          <t>20693</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>42330</t>
+          <t>41793</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>472869</t>
+          <t>472258</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>488950</t>
+          <t>488682</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>634090</t>
+          <t>634513</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>656918</t>
+          <t>657116</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1113369</t>
+          <t>1115782</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1141465</t>
+          <t>1142983</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>97,0%</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5873</t>
+          <t>4895</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6777</t>
+          <t>6751</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>961</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8557</t>
+          <t>7734</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38045</t>
+          <t>39023</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18512</t>
+          <t>18538</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>60650</t>
+          <t>61473</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>68243</t>
+          <t>68246</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>6824</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7231</t>
+          <t>6707</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7656</t>
+          <t>7220</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>5299</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1069</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>9652</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52974</t>
+          <t>53410</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11542</t>
+          <t>10884</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17873</t>
+          <t>17896</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>67444</t>
+          <t>68068</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77419</t>
+          <t>77450</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,38%</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>5035</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7158</t>
+          <t>6994</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>985</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>8875</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10867</t>
+          <t>11107</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7427</t>
+          <t>7542</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3112</t>
+          <t>3003</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13563</t>
+          <t>14179</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>106234</t>
+          <t>106321</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>115817</t>
+          <t>115931</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>44199</t>
+          <t>44626</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53468</t>
+          <t>53455</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>155611</t>
+          <t>155139</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>168000</t>
+          <t>168172</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6241</t>
+          <t>6511</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20860</t>
+          <t>22003</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5551</t>
+          <t>6343</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22122</t>
+          <t>21999</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9197</t>
+          <t>8534</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26657</t>
+          <t>26128</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2625</t>
+          <t>2544</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12954</t>
+          <t>12639</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14358</t>
+          <t>12879</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33696</t>
+          <t>33185</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>191878</t>
+          <t>190981</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>213508</t>
+          <t>213114</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>47141</t>
+          <t>47456</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>57470</t>
+          <t>57551</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>243028</t>
+          <t>245335</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>269202</t>
+          <t>268523</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,01%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>995</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>8153</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5409</t>
+          <t>5562</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18984</t>
+          <t>19706</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8350</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>23401</t>
+          <t>22906</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12217</t>
+          <t>11655</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17780</t>
+          <t>19190</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>37019</t>
+          <t>38247</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>23147</t>
+          <t>22820</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>44878</t>
+          <t>44581</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,32%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>86682</t>
+          <t>86907</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>98524</t>
+          <t>98619</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>138841</t>
+          <t>136772</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>160519</t>
+          <t>159677</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>230474</t>
+          <t>231700</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>256473</t>
+          <t>257001</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,29%</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11690</t>
+          <t>12640</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>30989</t>
+          <t>31630</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>13347</t>
+          <t>11852</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>32061</t>
+          <t>31442</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>21615</t>
+          <t>22731</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>43831</t>
+          <t>44181</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>21383</t>
+          <t>22047</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>43429</t>
+          <t>45508</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>327180</t>
+          <t>328235</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>355649</t>
+          <t>354849</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>330646</t>
+          <t>328716</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>357398</t>
+          <t>357084</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,02%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9510</t>
+          <t>9461</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>25637</t>
+          <t>26428</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>24791</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>48777</t>
+          <t>49304</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>38542</t>
+          <t>38402</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>66976</t>
+          <t>68982</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>19492</t>
+          <t>20223</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>42252</t>
+          <t>42855</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>55208</t>
+          <t>56238</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>88485</t>
+          <t>89651</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>81033</t>
+          <t>80397</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>120492</t>
+          <t>120932</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>499982</t>
+          <t>498251</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>527631</t>
+          <t>526582</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>615302</t>
+          <t>614160</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>654495</t>
+          <t>655332</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1123014</t>
+          <t>1124783</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1171562</t>
+          <t>1172205</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,06%</t>
         </is>
       </c>
     </row>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3938</t>
+          <t>3696</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8084</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8686</t>
+          <t>10041</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64709</t>
+          <t>64951</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>28804</t>
+          <t>28384</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>96849</t>
+          <t>95494</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>931</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7845</t>
+          <t>7915</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>904</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8379</t>
+          <t>8126</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6867</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>5618</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8784</t>
+          <t>8578</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43034</t>
+          <t>43539</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51423</t>
+          <t>51432</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11984</t>
+          <t>11970</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59146</t>
+          <t>58966</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68909</t>
+          <t>68809</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5757</t>
+          <t>5370</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5958</t>
+          <t>5912</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10226</t>
+          <t>11272</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7091</t>
+          <t>7905</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8665,7 +8665,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3814</t>
+          <t>3471</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14436</t>
+          <t>14877</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>107382</t>
+          <t>107310</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>117183</t>
+          <t>117132</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>39118</t>
+          <t>38304</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -8773,7 +8773,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>149487</t>
+          <t>150282</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>161446</t>
+          <t>161824</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -8958,7 +8958,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5854</t>
+          <t>5779</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8993,7 +8993,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6636</t>
+          <t>6665</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>825</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7999</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7723</t>
+          <t>8189</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20688</t>
+          <t>21581</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2358</t>
+          <t>2372</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15524</t>
+          <t>16079</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13549</t>
+          <t>13340</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>30868</t>
+          <t>31658</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,45%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>180835</t>
+          <t>180375</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>194411</t>
+          <t>194421</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>81514</t>
+          <t>82040</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>95575</t>
+          <t>95870</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>268655</t>
+          <t>267272</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>287123</t>
+          <t>287110</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5841</t>
+          <t>5832</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7976</t>
+          <t>9215</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>1601</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10027</t>
+          <t>11495</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2375</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12444</t>
+          <t>12060</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7131</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>23316</t>
+          <t>22377</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>11951</t>
+          <t>11406</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>30162</t>
+          <t>30501</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>130850</t>
+          <t>130564</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>141776</t>
+          <t>141735</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>132906</t>
+          <t>133715</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>150705</t>
+          <t>151513</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>269265</t>
+          <t>268661</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>289344</t>
+          <t>289815</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -9845,7 +9845,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9370</t>
+          <t>8768</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>27980</t>
+          <t>27105</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>9370</t>
+          <t>8768</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>27980</t>
+          <t>27105</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15370</t>
+          <t>14996</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>37873</t>
+          <t>38020</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>15370</t>
+          <t>14996</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>37873</t>
+          <t>38020</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>356363</t>
+          <t>355789</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>384772</t>
+          <t>384276</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>356363</t>
+          <t>355789</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>384772</t>
+          <t>384276</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,03%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3618</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14082</t>
+          <t>14759</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12524</t>
+          <t>11816</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>33445</t>
+          <t>32851</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>18696</t>
+          <t>18677</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>41477</t>
+          <t>42313</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>19176</t>
+          <t>18996</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>38092</t>
+          <t>38577</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>36355</t>
+          <t>37032</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>67687</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>60992</t>
+          <t>62161</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>101299</t>
+          <t>100023</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>543330</t>
+          <t>543780</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>564893</t>
+          <t>565130</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>681183</t>
+          <t>679639</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>717605</t>
+          <t>717522</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1231701</t>
+          <t>1234620</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1276778</t>
+          <t>1274505</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,46%</t>
         </is>
       </c>
     </row>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>927</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -11129,12 +11129,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3531</t>
+          <t>3309</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11154,7 +11154,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>490</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -11164,12 +11164,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2908</t>
+          <t>2389</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -11179,7 +11179,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11189,32 +11189,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>1417</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>310</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>3972</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -11232,27 +11232,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>106616</t>
+          <t>119474</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>104048</t>
+          <t>117092</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -11267,27 +11267,27 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>64788</t>
+          <t>74069</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62413</t>
+          <t>72170</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -11302,32 +11302,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>171404</t>
+          <t>193543</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>168661</t>
+          <t>190988</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>172566</t>
+          <t>194650</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -11345,17 +11345,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11380,17 +11380,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11415,17 +11415,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11497,32 +11497,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1533</t>
+          <t>1636</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>393</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4125</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11532,32 +11532,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1533</t>
+          <t>1636</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>397</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -11575,32 +11575,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>4134</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9594</t>
+          <t>9761</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11610,7 +11610,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>432</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -11620,12 +11620,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2405</t>
+          <t>2396</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11645,32 +11645,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4384</t>
+          <t>4566</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>1715</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9998</t>
+          <t>10344</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -11688,32 +11688,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>91049</t>
+          <t>100581</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>85404</t>
+          <t>94954</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>93656</t>
+          <t>103484</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>44963</t>
+          <t>53317</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42175</t>
+          <t>50401</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46364</t>
+          <t>54818</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>136012</t>
+          <t>153898</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>130384</t>
+          <t>147737</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>139239</t>
+          <t>157046</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -11801,17 +11801,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11836,17 +11836,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11871,17 +11871,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11918,7 +11918,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>820</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -11928,12 +11928,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2921</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11953,7 +11953,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>609</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -11963,12 +11963,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2985</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -11978,7 +11978,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11988,32 +11988,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1419</t>
+          <t>1429</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>346</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4143</t>
+          <t>4457</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -12031,102 +12031,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5750</t>
+          <t>5955</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2837</t>
+          <t>2808</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10704</t>
+          <t>11103</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>5,29%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,87%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>3636</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1535</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7402</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>6,27%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>12,77%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>9590</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>5682</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>15398</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
           <t>5,63%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10,49%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3178</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1346</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6421</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>6,02%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>12,16%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>8928</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>5412</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>14272</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>5,77%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -12144,32 +12144,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>95490</t>
+          <t>105696</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>90247</t>
+          <t>100665</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>98521</t>
+          <t>108997</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12179,32 +12179,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>49021</t>
+          <t>53726</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>45683</t>
+          <t>50147</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51105</t>
+          <t>56079</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>144511</t>
+          <t>159422</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>139402</t>
+          <t>153700</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>148388</t>
+          <t>163986</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -12257,17 +12257,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12292,17 +12292,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12374,32 +12374,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>5366</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2126</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9812</t>
+          <t>10252</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12409,32 +12409,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2085</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>726</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7191</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12444,32 +12444,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>7076</t>
+          <t>7519</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>3975</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13911</t>
+          <t>13647</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -12487,32 +12487,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12629</t>
+          <t>13861</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7836</t>
+          <t>8735</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18906</t>
+          <t>21204</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12522,32 +12522,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6168</t>
+          <t>6511</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>3338</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19037</t>
+          <t>10592</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12557,32 +12557,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>18797</t>
+          <t>20372</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6779</t>
+          <t>14141</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32650</t>
+          <t>28560</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -12600,32 +12600,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>220577</t>
+          <t>240779</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>213175</t>
+          <t>231692</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>226547</t>
+          <t>246925</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12635,32 +12635,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>318440</t>
+          <t>122216</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>301617</t>
+          <t>117818</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>325426</t>
+          <t>125931</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12670,32 +12670,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>539017</t>
+          <t>362995</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>521003</t>
+          <t>353884</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>555638</t>
+          <t>370595</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>94,81%</t>
         </is>
       </c>
     </row>
@@ -12713,17 +12713,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>238197</t>
+          <t>260006</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>238197</t>
+          <t>260006</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>238197</t>
+          <t>260006</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12748,17 +12748,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12783,17 +12783,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>564890</t>
+          <t>390886</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>564890</t>
+          <t>390886</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>564890</t>
+          <t>390886</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12830,7 +12830,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1170</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -12840,12 +12840,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4119</t>
+          <t>6727</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12865,32 +12865,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6356</t>
+          <t>6797</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3424</t>
+          <t>3589</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10156</t>
+          <t>11152</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12900,22 +12900,22 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>8045</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4306</t>
+          <t>4653</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12059</t>
+          <t>13816</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -12925,7 +12925,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -12943,32 +12943,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4423</t>
+          <t>4476</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8152</t>
+          <t>8466</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12978,32 +12978,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>21938</t>
+          <t>23677</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>16126</t>
+          <t>17238</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>28808</t>
+          <t>30398</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13013,32 +13013,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>26361</t>
+          <t>28153</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>20414</t>
+          <t>21316</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>33405</t>
+          <t>35593</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -13056,32 +13056,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>86413</t>
+          <t>95069</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>81707</t>
+          <t>90918</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>89045</t>
+          <t>97846</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13091,32 +13091,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>176015</t>
+          <t>188853</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>168830</t>
+          <t>180766</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>182604</t>
+          <t>195560</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13126,32 +13126,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>262428</t>
+          <t>283922</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>254300</t>
+          <t>274513</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>269352</t>
+          <t>291087</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,93%</t>
         </is>
       </c>
     </row>
@@ -13169,17 +13169,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13204,17 +13204,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>204309</t>
+          <t>219327</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>204309</t>
+          <t>219327</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>204309</t>
+          <t>219327</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13239,17 +13239,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>296315</t>
+          <t>320120</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>296315</t>
+          <t>320120</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>296315</t>
+          <t>320120</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -13321,32 +13321,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>10581</t>
+          <t>11119</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6413</t>
+          <t>6538</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16527</t>
+          <t>16901</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13356,32 +13356,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>10581</t>
+          <t>11119</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6540</t>
+          <t>6457</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16799</t>
+          <t>17068</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -13434,32 +13434,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>32827</t>
+          <t>35793</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>25112</t>
+          <t>27629</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>41146</t>
+          <t>45969</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13469,32 +13469,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>32827</t>
+          <t>35793</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>26011</t>
+          <t>28498</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>42126</t>
+          <t>46764</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
@@ -13512,7 +13512,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -13547,32 +13547,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>278264</t>
+          <t>298871</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>268759</t>
+          <t>287920</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>286785</t>
+          <t>307762</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13582,32 +13582,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>281468</t>
+          <t>302147</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>270663</t>
+          <t>291221</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>289628</t>
+          <t>311295</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,18%</t>
         </is>
       </c>
     </row>
@@ -13625,17 +13625,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13660,17 +13660,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>321672</t>
+          <t>345783</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>321672</t>
+          <t>345783</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>321672</t>
+          <t>345783</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13695,17 +13695,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>324876</t>
+          <t>349059</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>324876</t>
+          <t>349059</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>324876</t>
+          <t>349059</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13742,32 +13742,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>7434</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3585</t>
+          <t>3770</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13154</t>
+          <t>13436</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13777,32 +13777,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>21145</t>
+          <t>22314</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10330</t>
+          <t>15793</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>30601</t>
+          <t>30738</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13812,32 +13812,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>28135</t>
+          <t>29748</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>18707</t>
+          <t>22673</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>38083</t>
+          <t>39841</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -13855,32 +13855,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>27714</t>
+          <t>29353</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>20492</t>
+          <t>21480</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>36366</t>
+          <t>38935</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13890,32 +13890,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>65080</t>
+          <t>70537</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>31354</t>
+          <t>58225</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>84905</t>
+          <t>83091</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13925,32 +13925,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>92794</t>
+          <t>99890</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>58060</t>
+          <t>85029</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>113364</t>
+          <t>114523</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -13968,32 +13968,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>603349</t>
+          <t>664876</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>593665</t>
+          <t>654226</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>611223</t>
+          <t>673779</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14003,32 +14003,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>931490</t>
+          <t>791052</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>905685</t>
+          <t>777978</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>975032</t>
+          <t>804991</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14038,32 +14038,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1534838</t>
+          <t>1455929</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1509546</t>
+          <t>1439328</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1577612</t>
+          <t>1472167</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>92,85%</t>
         </is>
       </c>
     </row>
@@ -14081,17 +14081,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>638053</t>
+          <t>701663</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>638053</t>
+          <t>701663</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>638053</t>
+          <t>701663</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14116,17 +14116,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1017715</t>
+          <t>883904</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1017715</t>
+          <t>883904</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1017715</t>
+          <t>883904</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14151,17 +14151,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1655767</t>
+          <t>1585567</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1655767</t>
+          <t>1585567</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1655767</t>
+          <t>1585567</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
